--- a/Result/profitability/6199.xlsx
+++ b/Result/profitability/6199.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.22125</v>
+        <v>0.25</v>
       </c>
       <c r="N2" t="n">
-        <v>57.565</v>
+        <v>52.06875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0.10875</v>
+        <v>0.225</v>
       </c>
       <c r="N3" t="n">
-        <v>49.58625</v>
+        <v>43.3925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.71</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2075</v>
+        <v>0.33625</v>
       </c>
       <c r="N4" t="n">
-        <v>41.03375</v>
+        <v>34.69375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3875</v>
+        <v>0.51375</v>
       </c>
       <c r="N5" t="n">
-        <v>32.62375</v>
+        <v>26.68375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4125</v>
+        <v>0.41875</v>
       </c>
       <c r="N6" t="n">
-        <v>22.9625</v>
+        <v>21.91</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-2.97</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.05875000000000002</v>
+        <v>0.06624999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>15.98</v>
+        <v>15.45375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.43</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09375000000000003</v>
+        <v>-0.14</v>
       </c>
       <c r="N8" t="n">
-        <v>12.61125</v>
+        <v>9.71125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6199</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>207</v>
+      </c>
+      <c r="D75" t="n">
+        <v>143</v>
+      </c>
+      <c r="E75" t="n">
+        <v>64</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="G75" t="n">
+        <v>43</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>20.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>29</v>
+      </c>
+      <c r="J75" t="n">
+        <v>72</v>
+      </c>
+      <c r="K75" t="n">
+        <v>53</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="N75" t="n">
+        <v>59.53875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3032786885245902</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4273346841038865</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-6.3125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-47.52</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6045032438621041</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
